--- a/data/trans_dic/P1002-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1002-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 11,13</t>
+          <t>4,62; 10,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,71; 12,7</t>
+          <t>5,89; 12,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 13,55</t>
+          <t>6,17; 13,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,27</t>
+          <t>0,73; 4,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,83</t>
+          <t>4,97; 12,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,54; 24,95</t>
+          <t>15,29; 24,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,41; 24,3</t>
+          <t>15,31; 25,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,19</t>
+          <t>1,79; 5,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 10,22</t>
+          <t>5,6; 10,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,57; 17,33</t>
+          <t>11,59; 17,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 17,74</t>
+          <t>11,44; 17,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,93</t>
+          <t>1,55; 3,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 10,28</t>
+          <t>5,19; 10,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,98</t>
+          <t>5,4; 10,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,4</t>
+          <t>1,42; 4,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,69</t>
+          <t>4,62; 9,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,86; 18,08</t>
+          <t>11,75; 18,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,7; 18,49</t>
+          <t>11,68; 18,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,66</t>
+          <t>5,93; 10,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 13,29</t>
+          <t>8,74; 13,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,04; 12,93</t>
+          <t>9,17; 13,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 13,64</t>
+          <t>9,56; 13,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,07</t>
+          <t>4,05; 7,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 10,63</t>
+          <t>7,34; 10,72</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,42</t>
+          <t>0,3; 3,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 8,64</t>
+          <t>3,45; 8,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,05</t>
+          <t>0,97; 4,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,14</t>
+          <t>3,81; 8,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,2</t>
+          <t>1,92; 6,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,81; 15,21</t>
+          <t>7,91; 15,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,75</t>
+          <t>3,14; 8,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,82</t>
+          <t>4,76; 8,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,79</t>
+          <t>1,37; 3,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,04</t>
+          <t>6,33; 10,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,31</t>
+          <t>2,26; 5,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,67</t>
+          <t>4,68; 7,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,72</t>
+          <t>0,73; 3,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,22</t>
+          <t>3,96; 9,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 11,67</t>
+          <t>5,91; 11,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,94</t>
+          <t>3,62; 9,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,09</t>
+          <t>4,51; 9,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,59; 24,64</t>
+          <t>16,91; 24,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 23,17</t>
+          <t>14,87; 23,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 12,71</t>
+          <t>5,68; 13,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,19</t>
+          <t>2,92; 5,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,26; 16,24</t>
+          <t>11,43; 16,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,38; 16,52</t>
+          <t>11,22; 16,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,58</t>
+          <t>5,64; 10,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 9,84</t>
+          <t>3,71; 10,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,05</t>
+          <t>2,03; 7,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,4</t>
+          <t>1,91; 7,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,62</t>
+          <t>1,6; 5,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,04</t>
+          <t>2,95; 9,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,62; 22,8</t>
+          <t>12,59; 22,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 12,32</t>
+          <t>5,04; 12,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,25</t>
+          <t>6,57; 12,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,67</t>
+          <t>4,02; 8,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 14,4</t>
+          <t>8,15; 13,99</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,58</t>
+          <t>4,11; 9,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,03</t>
+          <t>4,67; 8,12</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,68</t>
+          <t>0,32; 3,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,34</t>
+          <t>4,21; 10,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,79; 11,69</t>
+          <t>5,15; 12,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,92</t>
+          <t>3,32; 7,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,45</t>
+          <t>1,98; 6,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,9; 14,85</t>
+          <t>7,38; 14,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,67; 17,0</t>
+          <t>9,25; 17,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,8</t>
+          <t>5,11; 9,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,15</t>
+          <t>1,38; 4,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,58; 11,31</t>
+          <t>6,91; 11,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,64; 13,62</t>
+          <t>7,56; 13,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,8</t>
+          <t>4,66; 7,8</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,15</t>
+          <t>3,49; 7,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,27</t>
+          <t>2,73; 6,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,66</t>
+          <t>4,37; 8,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,88</t>
+          <t>5,86; 10,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 11,95</t>
+          <t>7,44; 11,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 9,85</t>
+          <t>5,46; 9,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,51; 14,83</t>
+          <t>9,35; 14,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 13,92</t>
+          <t>4,66; 14,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,98</t>
+          <t>5,97; 8,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,33</t>
+          <t>4,67; 7,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,97</t>
+          <t>7,53; 10,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 11,4</t>
+          <t>5,98; 11,47</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,72</t>
+          <t>5,93; 9,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,97</t>
+          <t>6,44; 10,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,67</t>
+          <t>2,91; 5,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,46</t>
+          <t>1,97; 6,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,28; 11,38</t>
+          <t>7,26; 11,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,79; 17,84</t>
+          <t>12,68; 17,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,83</t>
+          <t>5,16; 8,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,22; 18,32</t>
+          <t>13,54; 18,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,14; 10,05</t>
+          <t>7,22; 10,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,44; 13,75</t>
+          <t>10,42; 13,79</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,93</t>
+          <t>4,47; 6,89</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,75; 11,35</t>
+          <t>5,76; 11,53</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,02</t>
+          <t>4,48; 6,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,75</t>
+          <t>5,85; 7,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,17</t>
+          <t>4,57; 6,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,32</t>
+          <t>4,17; 6,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,49; 9,52</t>
+          <t>7,53; 9,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,88; 15,19</t>
+          <t>12,89; 15,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,62; 11,71</t>
+          <t>9,66; 11,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,08</t>
+          <t>8,03; 11,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,53</t>
+          <t>6,26; 7,48</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,17</t>
+          <t>9,69; 11,13</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,7</t>
+          <t>7,39; 8,75</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,55</t>
+          <t>6,75; 8,64</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12750; 30386</t>
+          <t>12616; 29423</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16823; 37439</t>
+          <t>17369; 37268</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18035; 39790</t>
+          <t>18116; 39630</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2292; 13295</t>
+          <t>2281; 14060</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12653; 30846</t>
+          <t>12968; 31419</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44644; 71675</t>
+          <t>43907; 71759</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44477; 70154</t>
+          <t>44206; 72580</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5152; 15034</t>
+          <t>5185; 15144</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28810; 54562</t>
+          <t>29874; 54318</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67343; 100875</t>
+          <t>67437; 102271</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66228; 103305</t>
+          <t>66655; 101987</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9209; 23614</t>
+          <t>9317; 23415</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25593; 50664</t>
+          <t>25582; 49455</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28302; 55498</t>
+          <t>27286; 54452</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7189; 22123</t>
+          <t>7149; 21726</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25084; 50237</t>
+          <t>23952; 50242</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59788; 91095</t>
+          <t>59228; 92921</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61182; 96640</t>
+          <t>61071; 95859</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30444; 55750</t>
+          <t>31031; 56775</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44002; 68340</t>
+          <t>44937; 68852</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90176; 128925</t>
+          <t>91444; 130716</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95410; 140238</t>
+          <t>98266; 140918</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42747; 72530</t>
+          <t>41586; 72355</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74869; 109811</t>
+          <t>75798; 110677</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>944; 10911</t>
+          <t>942; 11467</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10731; 27984</t>
+          <t>11164; 28847</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2992; 12911</t>
+          <t>3083; 13826</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11008; 25712</t>
+          <t>12047; 26993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6304; 20805</t>
+          <t>6449; 20927</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26638; 51864</t>
+          <t>26960; 51268</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9492; 26057</t>
+          <t>10573; 27401</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16176; 30731</t>
+          <t>16584; 29677</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8962; 24775</t>
+          <t>8931; 25374</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42755; 73405</t>
+          <t>42075; 72713</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15762; 34788</t>
+          <t>14780; 34206</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31674; 50948</t>
+          <t>31129; 51571</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2566; 13360</t>
+          <t>2634; 12553</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15093; 34496</t>
+          <t>14798; 33946</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22851; 43187</t>
+          <t>21859; 43904</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10840; 27824</t>
+          <t>11256; 30000</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16294; 37497</t>
+          <t>16735; 35791</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64545; 95846</t>
+          <t>65771; 96924</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55662; 89737</t>
+          <t>57593; 90549</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24901; 60468</t>
+          <t>27027; 61882</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21651; 45186</t>
+          <t>21335; 43397</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85916; 123892</t>
+          <t>87187; 124140</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>86141; 125131</t>
+          <t>84952; 126756</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44695; 83309</t>
+          <t>44429; 82092</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7589; 20012</t>
+          <t>7533; 20335</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4765; 17125</t>
+          <t>4324; 16662</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3926; 15633</t>
+          <t>4026; 15814</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2873; 10039</t>
+          <t>2851; 9798</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6887; 20859</t>
+          <t>6117; 19728</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27718; 50062</t>
+          <t>27652; 50417</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10566; 26940</t>
+          <t>11027; 27743</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13428; 25474</t>
+          <t>13672; 25426</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16217; 35633</t>
+          <t>16513; 35513</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35681; 62217</t>
+          <t>35219; 60456</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17878; 36879</t>
+          <t>17660; 38936</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18459; 31076</t>
+          <t>18053; 31408</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>884; 9967</t>
+          <t>878; 8586</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12183; 28219</t>
+          <t>11503; 29105</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12615; 30768</t>
+          <t>13542; 31765</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8926; 21366</t>
+          <t>8946; 21133</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5116; 17929</t>
+          <t>5496; 18712</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19319; 41593</t>
+          <t>20668; 40424</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23667; 46421</t>
+          <t>25260; 48064</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13450; 25192</t>
+          <t>13133; 24284</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8148; 22772</t>
+          <t>7554; 22376</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36407; 62514</t>
+          <t>38232; 62162</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40959; 73018</t>
+          <t>40532; 69692</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25316; 41067</t>
+          <t>24532; 41076</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21970; 43966</t>
+          <t>21442; 44437</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18442; 41586</t>
+          <t>18117; 40302</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28405; 56860</t>
+          <t>28688; 55172</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36279; 67931</t>
+          <t>36585; 68259</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>45553; 76295</t>
+          <t>47493; 75575</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38892; 68220</t>
+          <t>37850; 66858</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>65756; 102511</t>
+          <t>64632; 100284</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>43177; 118246</t>
+          <t>39556; 120369</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>75371; 112595</t>
+          <t>74805; 110299</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63450; 99378</t>
+          <t>63301; 99140</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>101353; 147866</t>
+          <t>101439; 145134</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>82607; 167953</t>
+          <t>88071; 168947</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44060; 72323</t>
+          <t>44095; 73711</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>50404; 85372</t>
+          <t>50133; 85490</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22864; 44128</t>
+          <t>22650; 44029</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15737; 60032</t>
+          <t>18262; 60301</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>57035; 89178</t>
+          <t>56905; 88992</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>105392; 147004</t>
+          <t>104440; 146397</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41996; 72978</t>
+          <t>42652; 73945</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>94857; 131479</t>
+          <t>97168; 130631</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>108996; 153440</t>
+          <t>110203; 155330</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>167298; 220209</t>
+          <t>166998; 220993</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>72328; 111141</t>
+          <t>71772; 110584</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>94635; 186897</t>
+          <t>94856; 189787</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>146413; 197135</t>
+          <t>146756; 198797</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202429; 265576</t>
+          <t>200223; 262762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>157335; 209501</t>
+          <t>155036; 210026</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>143983; 218652</t>
+          <t>144095; 218060</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>253234; 321680</t>
+          <t>254321; 320284</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>458056; 540116</t>
+          <t>458486; 543955</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>341007; 415129</t>
+          <t>342362; 420308</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>297598; 405500</t>
+          <t>293952; 409591</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>416591; 501248</t>
+          <t>416760; 498152</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>674567; 780114</t>
+          <t>676277; 777108</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>512014; 603749</t>
+          <t>512495; 607279</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>477718; 608844</t>
+          <t>480796; 614848</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1002-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1002-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,78</t>
+          <t>4,61; 11,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,64</t>
+          <t>6,13; 12,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 13,49</t>
+          <t>6,11; 13,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,51</t>
+          <t>0,56; 3,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 12,05</t>
+          <t>4,7; 11,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,29; 24,98</t>
+          <t>15,06; 25,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,31; 25,14</t>
+          <t>15,43; 24,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,23</t>
+          <t>1,67; 4,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,17</t>
+          <t>5,38; 10,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,59; 17,57</t>
+          <t>11,49; 18,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,44; 17,51</t>
+          <t>11,72; 17,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,9</t>
+          <t>1,45; 3,29</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 10,03</t>
+          <t>4,95; 9,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 10,77</t>
+          <t>5,56; 10,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,32</t>
+          <t>1,45; 4,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,69</t>
+          <t>4,83; 9,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,75; 18,44</t>
+          <t>11,87; 17,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 18,34</t>
+          <t>11,9; 18,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 10,85</t>
+          <t>5,61; 10,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 13,39</t>
+          <t>8,39; 12,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,17; 13,11</t>
+          <t>9,11; 13,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,56; 13,7</t>
+          <t>9,47; 13,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,05</t>
+          <t>4,11; 7,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 10,72</t>
+          <t>7,37; 10,77</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,6</t>
+          <t>0,3; 3,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,9</t>
+          <t>3,27; 8,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,34</t>
+          <t>0,86; 4,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,54</t>
+          <t>4,0; 9,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,24</t>
+          <t>1,85; 5,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 15,03</t>
+          <t>7,8; 14,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,15</t>
+          <t>2,84; 8,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,51</t>
+          <t>4,85; 8,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,88</t>
+          <t>1,29; 3,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,93</t>
+          <t>6,29; 10,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,22</t>
+          <t>2,39; 5,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,76</t>
+          <t>4,97; 8,05</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,5</t>
+          <t>0,69; 3,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,08</t>
+          <t>3,91; 8,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 11,87</t>
+          <t>6,07; 11,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,64</t>
+          <t>3,39; 8,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,64</t>
+          <t>4,56; 9,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,91; 24,92</t>
+          <t>16,66; 24,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,87; 23,38</t>
+          <t>15,21; 23,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 13,01</t>
+          <t>8,77; 14,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,94</t>
+          <t>2,93; 6,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,43; 16,27</t>
+          <t>11,3; 16,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,74</t>
+          <t>11,51; 16,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,43</t>
+          <t>6,88; 11,05</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,0</t>
+          <t>3,62; 9,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,84</t>
+          <t>2,03; 8,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,49</t>
+          <t>1,89; 7,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,48</t>
+          <t>1,43; 4,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 9,5</t>
+          <t>3,37; 9,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,59; 22,96</t>
+          <t>12,49; 23,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,69</t>
+          <t>4,87; 11,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 12,22</t>
+          <t>6,07; 10,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,64</t>
+          <t>4,15; 8,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 13,99</t>
+          <t>8,12; 14,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,06</t>
+          <t>4,0; 8,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,12</t>
+          <t>4,33; 7,19</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,17</t>
+          <t>0,35; 3,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,21; 10,66</t>
+          <t>4,41; 10,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,15; 12,07</t>
+          <t>5,14; 12,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,84</t>
+          <t>3,25; 7,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,73</t>
+          <t>1,93; 6,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 14,44</t>
+          <t>7,34; 14,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,25; 17,6</t>
+          <t>8,32; 17,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,45</t>
+          <t>5,02; 9,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,08</t>
+          <t>1,55; 4,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,91; 11,24</t>
+          <t>6,6; 11,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 13,0</t>
+          <t>7,85; 13,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,8</t>
+          <t>4,7; 7,64</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,23</t>
+          <t>3,52; 7,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,08</t>
+          <t>2,7; 6,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,4</t>
+          <t>4,19; 8,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,93</t>
+          <t>5,64; 10,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,44; 11,84</t>
+          <t>7,34; 11,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,65</t>
+          <t>5,64; 9,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,35; 14,51</t>
+          <t>9,22; 14,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 14,17</t>
+          <t>11,26; 16,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,8</t>
+          <t>6,06; 8,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,31</t>
+          <t>4,66; 7,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,53; 10,77</t>
+          <t>7,46; 10,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,98; 11,47</t>
+          <t>9,11; 12,43</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,91</t>
+          <t>5,81; 9,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,99</t>
+          <t>6,58; 10,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,66</t>
+          <t>2,96; 5,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,49</t>
+          <t>4,29; 7,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,26; 11,36</t>
+          <t>7,29; 11,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,68; 17,77</t>
+          <t>12,77; 17,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,16; 8,95</t>
+          <t>5,18; 8,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,54; 18,2</t>
+          <t>13,11; 17,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,22; 10,17</t>
+          <t>7,02; 9,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,42; 13,79</t>
+          <t>10,31; 13,79</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,89</t>
+          <t>4,52; 6,76</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,76; 11,53</t>
+          <t>9,04; 11,61</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,07</t>
+          <t>4,53; 6,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,67</t>
+          <t>5,94; 7,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,19</t>
+          <t>4,66; 6,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,3</t>
+          <t>5,0; 6,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,53; 9,48</t>
+          <t>7,59; 9,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,89; 15,3</t>
+          <t>12,89; 15,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,86</t>
+          <t>9,53; 11,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,03; 11,19</t>
+          <t>9,98; 11,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,48</t>
+          <t>6,28; 7,57</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,69; 11,13</t>
+          <t>9,71; 11,18</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,75</t>
+          <t>7,42; 8,75</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,75; 8,64</t>
+          <t>7,72; 8,9</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>14548</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12616; 29423</t>
+          <t>12586; 30041</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17369; 37268</t>
+          <t>18058; 37968</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18116; 39630</t>
+          <t>17936; 38426</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2281; 14060</t>
+          <t>1783; 10794</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12968; 31419</t>
+          <t>12264; 30913</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43907; 71759</t>
+          <t>43246; 72125</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44206; 72580</t>
+          <t>44554; 70855</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5185; 15144</t>
+          <t>5264; 14611</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29874; 54318</t>
+          <t>28722; 54596</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67437; 102271</t>
+          <t>66859; 104995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66655; 101987</t>
+          <t>68285; 101383</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9317; 23415</t>
+          <t>9231; 20902</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35776</t>
+          <t>37055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55632</t>
+          <t>57369</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91408</t>
+          <t>94424</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25582; 49455</t>
+          <t>24410; 49039</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27286; 54452</t>
+          <t>28087; 54286</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7149; 21726</t>
+          <t>7276; 21770</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23952; 50242</t>
+          <t>25619; 51421</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59228; 92921</t>
+          <t>59831; 90633</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61071; 95859</t>
+          <t>62180; 94726</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31031; 56775</t>
+          <t>29362; 55327</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44937; 68852</t>
+          <t>45768; 70294</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91444; 130716</t>
+          <t>90796; 130057</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98266; 140918</t>
+          <t>97403; 140137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41586; 72355</t>
+          <t>42153; 71794</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75798; 110677</t>
+          <t>79344; 115976</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22609</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40280</t>
+          <t>42435</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>942; 11467</t>
+          <t>941; 11258</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11164; 28847</t>
+          <t>10598; 27861</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3083; 13826</t>
+          <t>2753; 13654</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12047; 26993</t>
+          <t>12636; 28732</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6449; 20927</t>
+          <t>6212; 19573</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26960; 51268</t>
+          <t>26614; 50724</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10573; 27401</t>
+          <t>9554; 27614</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16584; 29677</t>
+          <t>17269; 30535</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8931; 25374</t>
+          <t>8407; 25204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42075; 72713</t>
+          <t>41818; 71249</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14780; 34206</t>
+          <t>15644; 36196</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31129; 51571</t>
+          <t>33371; 54087</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>42934</t>
+          <t>47996</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61396</t>
+          <t>68975</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2634; 12553</t>
+          <t>2466; 12797</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14798; 33946</t>
+          <t>14636; 33258</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21859; 43904</t>
+          <t>22468; 43147</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11256; 30000</t>
+          <t>12604; 33042</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16735; 35791</t>
+          <t>16933; 37103</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65771; 96924</t>
+          <t>64786; 96781</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57593; 90549</t>
+          <t>58887; 90193</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27027; 61882</t>
+          <t>37005; 62292</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21335; 43397</t>
+          <t>21383; 45113</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87187; 124140</t>
+          <t>86183; 124169</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84952; 126756</t>
+          <t>87161; 124616</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44429; 82092</t>
+          <t>54629; 87724</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24169</t>
+          <t>24302</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7533; 20335</t>
+          <t>7359; 19391</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4324; 16662</t>
+          <t>4319; 17039</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4026; 15814</t>
+          <t>3982; 15495</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2851; 9798</t>
+          <t>2937; 10102</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6117; 19728</t>
+          <t>6991; 20534</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27652; 50417</t>
+          <t>27426; 50845</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11027; 27743</t>
+          <t>10654; 25549</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13672; 25426</t>
+          <t>13759; 24450</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16513; 35513</t>
+          <t>17076; 35822</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35219; 60456</t>
+          <t>35116; 62256</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17660; 38936</t>
+          <t>17194; 37092</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18053; 31408</t>
+          <t>18715; 31060</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32532</t>
+          <t>32443</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>878; 8586</t>
+          <t>936; 9132</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11503; 29105</t>
+          <t>12047; 29435</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13542; 31765</t>
+          <t>13530; 31868</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8946; 21133</t>
+          <t>8800; 21346</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5496; 18712</t>
+          <t>5378; 18844</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20668; 40424</t>
+          <t>20561; 39670</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25260; 48064</t>
+          <t>22724; 46617</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13133; 24284</t>
+          <t>13252; 24725</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7554; 22376</t>
+          <t>8508; 23112</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38232; 62162</t>
+          <t>36522; 63113</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40532; 69692</t>
+          <t>42074; 71683</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24532; 41076</t>
+          <t>25122; 40833</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50151</t>
+          <t>55382</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>86078</t>
+          <t>103814</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>136229</t>
+          <t>159196</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21442; 44437</t>
+          <t>21653; 44019</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18117; 40302</t>
+          <t>17925; 41683</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28688; 55172</t>
+          <t>27494; 54904</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36585; 68259</t>
+          <t>40623; 75157</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>47493; 75575</t>
+          <t>46874; 75350</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37850; 66858</t>
+          <t>39110; 68848</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>64632; 100284</t>
+          <t>63732; 100007</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>39556; 120369</t>
+          <t>86936; 123912</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>74805; 110299</t>
+          <t>75997; 111956</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63301; 99140</t>
+          <t>63129; 100941</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>101439; 145134</t>
+          <t>100493; 145028</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>88071; 168947</t>
+          <t>135927; 185492</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>45498</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>112318</t>
+          <t>123954</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>152062</t>
+          <t>169452</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44095; 73711</t>
+          <t>43181; 72510</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>50133; 85490</t>
+          <t>51168; 84870</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22650; 44029</t>
+          <t>23072; 44489</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18262; 60301</t>
+          <t>34258; 59910</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>56905; 88992</t>
+          <t>57154; 89297</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>104440; 146397</t>
+          <t>105227; 146295</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>42652; 73945</t>
+          <t>42794; 74238</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>97168; 130631</t>
+          <t>109011; 143441</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>110203; 155330</t>
+          <t>107186; 151029</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>166998; 220993</t>
+          <t>165152; 220846</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>71772; 110584</t>
+          <t>72592; 108413</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>94856; 189787</t>
+          <t>147254; 189251</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>187834</t>
+          <t>202972</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>365157</t>
+          <t>402803</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>552991</t>
+          <t>605775</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>146756; 198797</t>
+          <t>148464; 198912</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>200223; 262762</t>
+          <t>203429; 264601</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>155036; 210026</t>
+          <t>158177; 210644</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>144095; 218060</t>
+          <t>176467; 233558</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>254321; 320284</t>
+          <t>256407; 320052</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>458486; 543955</t>
+          <t>458375; 538013</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>342362; 420308</t>
+          <t>337941; 419802</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>293952; 409591</t>
+          <t>372575; 438334</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>416760; 498152</t>
+          <t>417963; 503940</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>676277; 777108</t>
+          <t>677517; 780673</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>512495; 607279</t>
+          <t>514784; 607076</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>480796; 614848</t>
+          <t>560588; 646768</t>
         </is>
       </c>
     </row>
